--- a/Questions - Round 5.xlsx
+++ b/Questions - Round 5.xlsx
@@ -4519,8 +4519,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff0b0af6195b7500cf034195288be193">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c14c416c1ab46b49649d30a0f512b68e" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -4565,7 +4565,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4592,8 +4592,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4701,19 +4701,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D680CD0A-F5CD-4EED-BD0E-59EFA7D82E33}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C7F3E58-7FBA-4511-A0E7-E380379B574D}"/>
 </file>